--- a/ics_topologies/oil_&_gas_pipeline/oil_&_gas_pipeline.xlsx
+++ b/ics_topologies/oil_&_gas_pipeline/oil_&_gas_pipeline.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R30"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,65 +445,70 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>purdue_level</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>criticality</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>vendor</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ip</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>cvss_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>exposed</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>patched</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>consequence_severity</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>awareness</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>privilege</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>p_base_override</t>
         </is>
@@ -537,49 +542,54 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Protects control center</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Palo Alto</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>PA-5250</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -609,49 +619,54 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Core switch</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Cisco</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Catalyst 9300</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -681,49 +696,54 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>Pipeline SCADA</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Schneider</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>OASyS DNA</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -753,49 +773,54 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>Pipeline data historian</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>OSIsoft</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>PI Server</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -825,49 +850,54 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>Operator console</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Schneider</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>ClearSCADA</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -897,49 +927,54 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>Configuration station</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Dell</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Precision 7920</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -969,49 +1004,54 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>RTU for pump station A</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Control Microsystems</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>SCADAPack 470</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1041,49 +1081,54 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>RTU for pump station B</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Control Microsystems</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>SCADAPack 470</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1113,49 +1158,54 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>RTU for block valve site</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Control Microsystems</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>SCADAPack 470</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1185,49 +1235,54 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>RTU for custody transfer</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Control Microsystems</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>SCADAPack 470</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1257,49 +1312,54 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>Industrial switch for station A</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>SCALANCE XM408</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1329,49 +1389,54 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>Industrial switch for station B</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>SCALANCE XM408</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1401,37 +1466,42 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>Centrifugal pump</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Sulzer</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Z6</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
@@ -1465,37 +1535,42 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>Standby pump</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Sulzer</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Z6</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
@@ -1529,49 +1604,54 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>Variable frequency drive for pump</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>ABB</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>ACS880</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1601,37 +1681,42 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>Motor-operated valve</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Emerson</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Fisher V500</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
@@ -1665,37 +1750,42 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>Discharge pressure</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Emerson</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Rosemount 3051</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -1729,37 +1819,42 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>Ultrasonic flow meter</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Emerson</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Daniel 3410</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -1793,37 +1888,42 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>Product temperature</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Emerson</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Rosemount 214</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -1857,37 +1957,42 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>Centrifugal pump</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Sulzer</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Z6</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
@@ -1921,49 +2026,54 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>VFD for pump B</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>ABB</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>ACS880</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1993,37 +2103,42 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>Motor-operated valve</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Emerson</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Fisher V500</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
@@ -2057,37 +2172,42 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>Discharge pressure</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Emerson</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Rosemount 3051</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -2121,37 +2241,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>Ultrasonic flow meter</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Emerson</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Daniel 3410</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -2185,37 +2310,42 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>Emergency block valve</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Emerson</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Fisher V500</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
@@ -2249,37 +2379,42 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>Pressure at valve site</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Emerson</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Rosemount 3051</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -2313,37 +2448,42 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>Custody transfer meter</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Emerson</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Daniel 3410</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -2377,37 +2517,42 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>Product density</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Emerson</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Micro Motion</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -2441,41 +2586,46 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>Dispatcher monitoring pipeline operations</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>operator</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2488,7 +2638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2522,6 +2672,16 @@
           <t>trust</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>firewalled</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2554,6 +2714,12 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2586,6 +2752,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2618,6 +2786,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2650,6 +2820,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2682,6 +2854,8 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2714,6 +2888,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2746,6 +2922,8 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2778,6 +2956,8 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2810,6 +2990,8 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2842,6 +3024,8 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2874,6 +3058,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2906,6 +3092,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2938,6 +3126,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2970,6 +3160,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3002,6 +3194,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3034,6 +3228,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3066,6 +3262,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3098,6 +3296,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3130,6 +3330,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3162,6 +3364,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3194,6 +3398,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3226,6 +3432,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3258,6 +3466,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3290,6 +3500,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3322,6 +3534,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3354,6 +3568,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3386,6 +3602,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3418,6 +3636,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
